--- a/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62619</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44345</t>
+          <t>44787</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85719</t>
+          <t>87919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53704</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82263</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71646</t>
+          <t>70749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93608</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132370</t>
+          <t>131382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169647</t>
+          <t>168690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64028</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94686</t>
+          <t>95027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68699</t>
+          <t>68616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>90915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141807</t>
+          <t>140993</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>179623</t>
+          <t>177640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47947</t>
+          <t>47304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>77965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>50525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>63363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90206</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49588</t>
+          <t>53347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49472</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50717</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90238</t>
+          <t>92238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62630</t>
+          <t>62676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98899</t>
+          <t>98779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88850</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>118028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161378</t>
+          <t>161516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207041</t>
+          <t>207420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136766</t>
+          <t>135757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>182476</t>
+          <t>178259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>105506</t>
+          <t>106589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137906</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>251390</t>
+          <t>252231</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>308053</t>
+          <t>305864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78396</t>
+          <t>78075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57300</t>
+          <t>56686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>81730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109671</t>
+          <t>113000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150307</t>
+          <t>150317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>44289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>76879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>43709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79611</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>79947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142317</t>
+          <t>139997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381164</t>
+          <t>379806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193511</t>
+          <t>192475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>529364</t>
+          <t>509200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87004</t>
+          <t>87081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>120992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>21422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154094</t>
+          <t>154370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74168</t>
+          <t>81500</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>267347</t>
+          <t>268836</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39434</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59315</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34639</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48402</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33856</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67228</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>62282</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93696</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>106592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136725</t>
+          <t>137117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>176143</t>
+          <t>173623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>220543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>114920</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151954</t>
+          <t>151069</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131182</t>
+          <t>132803</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>165866</t>
+          <t>169061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>256229</t>
+          <t>255615</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>305651</t>
+          <t>307358</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84884</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>46995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>107199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147062</t>
+          <t>148951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72219</t>
+          <t>72739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>69559</t>
+          <t>68863</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96888</t>
+          <t>96029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119159</t>
+          <t>117781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156844</t>
+          <t>159041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92388</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>159074</t>
+          <t>155621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>63278</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266998</t>
+          <t>269705</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>253830</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320807</t>
+          <t>320243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>435819</t>
+          <t>433599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>881134</t>
+          <t>927840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>712041</t>
+          <t>709056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1289526</t>
+          <t>1349015</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>436103</t>
+          <t>439416</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>515582</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>275744</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>502509</t>
+          <t>500321</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>687056</t>
+          <t>655904</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>987498</t>
+          <t>984342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>217935</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>224052</t>
+          <t>225418</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>287399</t>
+          <t>276518</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>423509</t>
+          <t>424557</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>160446</t>
+          <t>162978</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>110261</t>
+          <t>102194</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>205961</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>228196</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>343288</t>
+          <t>346830</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41204</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59244</t>
+          <t>60531</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44787</t>
+          <t>46441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87919</t>
+          <t>84419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>77625</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54398</t>
+          <t>62732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82516</t>
+          <t>94668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82095</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70749</t>
+          <t>77809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>102442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149598</t>
+          <t>166875</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131382</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>168690</t>
+          <t>187707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>85670</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>71507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95027</t>
+          <t>102256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>83890</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90915</t>
+          <t>95746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>159041</t>
+          <t>169559</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140993</t>
+          <t>150332</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177640</t>
+          <t>190520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47304</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>32492</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>41986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64420</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77965</t>
+          <t>84848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>31551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50525</t>
+          <t>54528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>40542</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46938</t>
+          <t>51845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75862</t>
+          <t>83073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>68226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90895</t>
+          <t>98995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>249255</t>
+          <t>271869</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>249255</t>
+          <t>271869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>249255</t>
+          <t>271869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>258910</t>
+          <t>279187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>258910</t>
+          <t>279187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258910</t>
+          <t>279187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>508165</t>
+          <t>551056</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>508165</t>
+          <t>551056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>508165</t>
+          <t>551056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53347</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>40035</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>54725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67563</t>
+          <t>67282</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92238</t>
+          <t>88087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80140</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62676</t>
+          <t>75345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>112483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102890</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88445</t>
+          <t>103050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118028</t>
+          <t>136175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>183031</t>
+          <t>213035</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161516</t>
+          <t>190651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207420</t>
+          <t>238815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158189</t>
+          <t>167643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135757</t>
+          <t>149028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178259</t>
+          <t>190157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>121028</t>
+          <t>130527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106589</t>
+          <t>113998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>147937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>279217</t>
+          <t>298170</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252231</t>
+          <t>272136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>305864</t>
+          <t>325943</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61890</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47094</t>
+          <t>54946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78075</t>
+          <t>86310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68169</t>
+          <t>76321</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>63543</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81730</t>
+          <t>90292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>130060</t>
+          <t>145783</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>125699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150317</t>
+          <t>168059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>42979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34069</t>
+          <t>40069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44289</t>
+          <t>51546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61402</t>
+          <t>70630</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76879</t>
+          <t>88188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>358089</t>
+          <t>388417</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>358089</t>
+          <t>388417</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>358089</t>
+          <t>388417</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>363182</t>
+          <t>406482</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>363182</t>
+          <t>406482</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>363182</t>
+          <t>406482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>721271</t>
+          <t>794900</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>721271</t>
+          <t>794900</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>721271</t>
+          <t>794900</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43709</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>50056</t>
+          <t>53280</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80246</t>
+          <t>70971</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>77050</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47169</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79947</t>
+          <t>95073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>281552</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139997</t>
+          <t>83930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379806</t>
+          <t>113160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>343730</t>
+          <t>175092</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192475</t>
+          <t>152729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>509200</t>
+          <t>197176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103738</t>
+          <t>113387</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87081</t>
+          <t>95021</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120992</t>
+          <t>130705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74993</t>
+          <t>85718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154370</t>
+          <t>99152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>178731</t>
+          <t>199104</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81500</t>
+          <t>177690</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>268836</t>
+          <t>221774</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>20614</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>43046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>44093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56286</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>48853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>77651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>31919</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>25439</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52589</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239317</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239317</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239317</t>
+          <t>266447</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>421404</t>
+          <t>257116</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>421404</t>
+          <t>257116</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>421404</t>
+          <t>257116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>660721</t>
+          <t>523563</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>660721</t>
+          <t>523563</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>660721</t>
+          <t>523563</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>28769</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49847</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>46835</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>37267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>76039</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62282</t>
+          <t>74654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95172</t>
+          <t>108418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>121133</t>
+          <t>131892</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106592</t>
+          <t>115386</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137117</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>197172</t>
+          <t>221623</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>173623</t>
+          <t>198719</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220543</t>
+          <t>248184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>132667</t>
+          <t>138549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114920</t>
+          <t>118701</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151069</t>
+          <t>157201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>147846</t>
+          <t>155222</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>132803</t>
+          <t>138033</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>169061</t>
+          <t>172977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>280513</t>
+          <t>293771</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>255615</t>
+          <t>266532</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>307358</t>
+          <t>319352</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>67340</t>
+          <t>73205</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>58938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84508</t>
+          <t>93697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>59445</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46995</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>126785</t>
+          <t>137955</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107199</t>
+          <t>120440</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148951</t>
+          <t>162651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44445</t>
+          <t>50691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72739</t>
+          <t>82839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81347</t>
+          <t>93519</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68863</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96029</t>
+          <t>109184</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>158958</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>117781</t>
+          <t>139144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159041</t>
+          <t>184311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>362363</t>
+          <t>395694</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>362363</t>
+          <t>395694</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>362363</t>
+          <t>395694</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>426728</t>
+          <t>467699</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>426728</t>
+          <t>467699</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>426728</t>
+          <t>467699</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>789091</t>
+          <t>863392</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>789091</t>
+          <t>863392</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>789091</t>
+          <t>863392</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>113722</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>155621</t>
+          <t>145069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63278</t>
+          <t>100858</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>223698</t>
+          <t>232178</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>269705</t>
+          <t>266867</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>285861</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>255865</t>
+          <t>307497</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320243</t>
+          <t>376985</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>587670</t>
+          <t>438715</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>433599</t>
+          <t>407506</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>927840</t>
+          <t>467763</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>873531</t>
+          <t>776625</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>709056</t>
+          <t>732929</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1349015</t>
+          <t>825430</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>475019</t>
+          <t>505249</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>439416</t>
+          <t>468699</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>515582</t>
+          <t>542651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>422483</t>
+          <t>455357</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261939</t>
+          <t>426477</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>500321</t>
+          <t>484250</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>897502</t>
+          <t>960606</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>655904</t>
+          <t>912501</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>984342</t>
+          <t>1006880</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>217935</t>
+          <t>241575</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>185868</t>
+          <t>205796</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111900</t>
+          <t>183257</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>225418</t>
+          <t>228537</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>377551</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>379491</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>424557</t>
+          <t>452488</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3905,27 +3905,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>154408</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>117195</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>178212</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>192161</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102194</t>
+          <t>171088</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>205036</t>
+          <t>215672</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>306967</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>315136</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>377139</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
